--- a/diseases/d248/2026-2029.xlsx
+++ b/diseases/d248/2026-2029.xlsx
@@ -3033,6 +3033,396 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Powassan virus</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Ontario IDTO Powassan virus disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3066,7 +3456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3539,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3159,7 +3549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -3179,7 +3569,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d248/2026-2029.xlsx
+++ b/diseases/d248/2026-2029.xlsx
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3418,6 +3418,396 @@
         </is>
       </c>
       <c r="BC15" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Powassan virus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Ontario IDTO Powassan virus disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -3456,7 +3846,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3929,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3549,7 +3939,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -3569,7 +3959,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3601,7 +3991,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d248/2026-2029.xlsx
+++ b/diseases/d248/2026-2029.xlsx
@@ -770,11 +770,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -782,30 +777,26 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -872,7 +863,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -907,12 +898,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -921,34 +912,9 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Powassan virus</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -956,90 +922,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1141,12 +1045,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1160,11 +1064,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1172,30 +1071,26 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1262,7 +1157,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1297,12 +1192,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1311,34 +1206,9 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Powassan virus</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1346,90 +1216,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1531,61 +1339,52 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1652,17 +1451,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1687,112 +1486,40 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Powassan virus</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -1811,7 +1538,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1824,42 +1551,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -1886,17 +1613,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1921,34 +1648,110 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -1967,7 +1770,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1980,42 +1783,42 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2042,17 +1845,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2077,112 +1880,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Powassan virus</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -2201,7 +1929,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2214,42 +1942,42 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2004,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2311,7 +2039,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2325,20 +2053,96 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+      <c r="P10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:US-MA:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -2357,7 +2161,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -2370,42 +2174,42 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2236,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2467,12 +2271,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2481,34 +2285,9 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Powassan virus</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2516,90 +2295,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>1</v>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2671,12 +2388,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2701,7 +2418,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2715,19 +2432,25 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2747,7 +2470,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT12" t="n">
@@ -2760,42 +2483,42 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2550,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2857,7 +2580,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2871,24 +2594,27 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>Arboviral diseases, Powassan virus disease</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Powassan virus</t>
+          <t>Arboviral diseases, Powassan virus disease</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2903,7 +2629,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2913,7 +2639,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>country:CA-ON:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2933,7 +2659,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>non_additive</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2948,12 +2674,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
+          <t>source-current</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2981,7 +2702,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT13" t="n">
@@ -2994,42 +2715,42 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -3061,12 +2782,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3091,12 +2812,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3105,19 +2826,17 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -3127,7 +2846,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3137,55 +2856,55 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3217,12 +2936,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3247,12 +2966,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3261,24 +2980,27 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>Arboviral diseases, Powassan virus disease</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Powassan virus</t>
+          <t>Arboviral diseases, Powassan virus disease</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3293,7 +3015,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -3303,7 +3025,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>country:CA-ON:national</t>
+          <t>country:US-NY:national</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -3323,7 +3045,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>non_additive</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -3338,12 +3060,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
+          <t>source-current</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -3361,7 +3078,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3371,55 +3088,55 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
+          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3198,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3500,11 +3217,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3512,30 +3224,26 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3602,214 +3310,1687 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CA-ON</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Ontario, Canada</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>D248</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Powassan virus disease</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>波瓦桑病毒病</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Powassan virus</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Ontario IDTO Powassan virus disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
         <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="AN17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="AQ19" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_POWASSAN_VIRUS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Public Health Ontario IDTO Monthly</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>Public Health Ontario IDTO Monthly</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>US-NY</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>US-NY</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:US-NY:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>US-NY</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>powassan-virus-disease</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>US-NY</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D248</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>波瓦桑病毒病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Arboviral diseases, Powassan virus disease</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:US-NY:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3846,7 +5027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3929,7 +5110,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -3939,7 +5120,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -3991,7 +5172,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d248/2026-2029.xlsx
+++ b/diseases/d248/2026-2029.xlsx
@@ -765,11 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -782,23 +777,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -912,11 +897,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -929,23 +909,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1059,11 +1029,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1076,23 +1041,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1206,11 +1161,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1223,23 +1173,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1353,11 +1293,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1370,23 +1305,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -2285,11 +2210,6 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2302,23 +2222,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -3212,11 +3122,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3229,23 +3134,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -3359,11 +3254,6 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3376,22 +3266,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>

--- a/diseases/d248/2026-2029.xlsx
+++ b/diseases/d248/2026-2029.xlsx
@@ -1431,11 +1431,6 @@
       <c r="R7" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
@@ -1453,12 +1448,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1468,11 +1458,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1538,17 +1523,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>US-MA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Massachusetts, United States</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1595,89 +1580,11 @@
           <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN8" t="b">
-        <v>1</v>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1685,12 +1592,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1701,11 +1603,6 @@
       <c r="AT8" t="n">
         <v>1</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1718,32 +1615,32 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1672,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1805,12 +1702,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1819,90 +1716,63 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1929,17 +1799,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>US-MA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Massachusetts, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1964,12 +1834,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1981,94 +1851,19 @@
       <c r="P10" t="n">
         <v>1</v>
       </c>
+      <c r="R10" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>country:US-MA:national</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN10" t="b">
-        <v>1</v>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2076,12 +1871,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2092,11 +1882,6 @@
       <c r="AT10" t="n">
         <v>1</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2109,32 +1894,32 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2166,12 +1951,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2196,7 +1981,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2210,14 +1995,22 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2225,48 +2018,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2095,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2328,12 +2125,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2342,93 +2139,63 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2455,17 +2222,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2490,12 +2257,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2504,163 +2271,63 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2359,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>US-NY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>New York, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2722,12 +2389,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2739,9 +2406,12 @@
       <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="R14" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2756,26 +2426,16 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2789,32 +2449,32 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2501,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2876,12 +2536,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2898,89 +2558,11 @@
           <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>country:US-NY:national</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN15" t="b">
-        <v>1</v>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2988,26 +2570,16 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3078,12 +2650,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3108,12 +2680,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3122,14 +2694,25 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -3137,48 +2720,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -3210,12 +2797,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3240,12 +2827,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3254,14 +2841,22 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
@@ -3269,1606 +2864,50 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>US-NY</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>New York, United States</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>US-NY</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>New York, United States</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>country:US-NY:national</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>nndss_api; nhss_hiv</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>api; api</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>US-NY</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>New York, United States</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA24" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>powassan-virus-disease</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>US-NY</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>New York, United States</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>D248</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>波瓦桑病毒病</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Arboviral diseases, Powassan virus disease</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>country:US-NY:national</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>HOLD_US_a1bb05668cb509d11c2247438015; HOLD_US_a7b06d1061e60d3aa13e5b2a310e</t>
-        </is>
-      </c>
-      <c r="AT25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA25" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -5000,7 +3039,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -5020,7 +3059,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5030,7 +3069,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d248/2026-2029.xlsx
+++ b/diseases/d248/2026-2029.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -777,13 +782,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -897,6 +912,11 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -909,13 +929,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1029,6 +1059,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1041,13 +1076,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1161,6 +1206,11 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1173,13 +1223,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1293,6 +1353,11 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1305,13 +1370,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -1716,6 +1791,11 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1728,13 +1808,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -2139,6 +2229,11 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2151,13 +2246,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -2271,6 +2376,11 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2283,12 +2393,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
